--- a/research/traditional_assets/database/data/egypt/egypt_power.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_power.xlsx
@@ -588,43 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.294</v>
+        <v>0.333</v>
+      </c>
+      <c r="E2">
+        <v>0.778</v>
       </c>
       <c r="G2">
-        <v>-0.02961939840392879</v>
+        <v>0.02233589087809037</v>
       </c>
       <c r="H2">
-        <v>-0.02961939840392879</v>
+        <v>0.02233589087809037</v>
       </c>
       <c r="I2">
-        <v>0.002679558011049723</v>
+        <v>-0.03466894003978403</v>
       </c>
       <c r="J2">
-        <v>0.002679558011049723</v>
+        <v>-0.0314909538694705</v>
       </c>
       <c r="K2">
-        <v>7.49</v>
+        <v>14.1</v>
       </c>
       <c r="L2">
-        <v>0.02298956414978514</v>
+        <v>0.04006820119352089</v>
       </c>
       <c r="M2">
-        <v>4.04</v>
+        <v>3.63</v>
       </c>
       <c r="N2">
-        <v>0.03662737987307343</v>
+        <v>0.02510373443983403</v>
       </c>
       <c r="O2">
-        <v>0.5393858477970628</v>
+        <v>0.2574468085106383</v>
       </c>
       <c r="P2">
-        <v>4.04</v>
+        <v>3.63</v>
       </c>
       <c r="Q2">
-        <v>0.03662737987307343</v>
+        <v>0.02510373443983403</v>
       </c>
       <c r="R2">
-        <v>0.5393858477970628</v>
+        <v>0.2574468085106383</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,70 +636,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.62</v>
+        <v>11.5</v>
       </c>
       <c r="V2">
-        <v>0.02375339981867634</v>
+        <v>0.07952973720608576</v>
       </c>
       <c r="W2">
-        <v>0.05404040404040404</v>
+        <v>0.09873949579831932</v>
       </c>
       <c r="X2">
-        <v>0.08539939409945423</v>
+        <v>0.1106899086540348</v>
       </c>
       <c r="Y2">
-        <v>-0.03135899005905018</v>
+        <v>-0.01195041285571549</v>
       </c>
       <c r="Z2">
-        <v>1.542613636363636</v>
+        <v>1.811303273625695</v>
       </c>
       <c r="AA2">
-        <v>0.004133522727272728</v>
+        <v>-0.05703966783336764</v>
       </c>
       <c r="AB2">
-        <v>0.07519238782418403</v>
+        <v>0.1098294225581551</v>
       </c>
       <c r="AC2">
-        <v>-0.0710588650969113</v>
+        <v>-0.1668690903915228</v>
       </c>
       <c r="AD2">
-        <v>54.1</v>
+        <v>8.27</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>54.1</v>
+        <v>8.27</v>
       </c>
       <c r="AG2">
-        <v>51.48</v>
+        <v>-3.23</v>
       </c>
       <c r="AH2">
-        <v>0.3290754257907543</v>
+        <v>0.0540982534179368</v>
       </c>
       <c r="AI2">
-        <v>0.2747587607922803</v>
+        <v>0.0615923139941908</v>
       </c>
       <c r="AJ2">
-        <v>0.3182099146989739</v>
+        <v>-0.02284784607766853</v>
       </c>
       <c r="AK2">
-        <v>0.2649783817171093</v>
+        <v>-0.02630935896391627</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-5.53</v>
+        <v>-0.862</v>
       </c>
       <c r="AN2">
-        <v>10.90725806451613</v>
+        <v>-1.001210653753027</v>
       </c>
       <c r="AP2">
-        <v>10.37903225806452</v>
+        <v>0.391041162227603</v>
       </c>
       <c r="AQ2">
-        <v>-0.1578661844484629</v>
+        <v>14.15313225058004</v>
       </c>
     </row>
     <row r="3">
@@ -716,43 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.294</v>
+        <v>0.333</v>
+      </c>
+      <c r="E3">
+        <v>0.778</v>
       </c>
       <c r="G3">
-        <v>-0.02961939840392879</v>
+        <v>0.02233589087809037</v>
       </c>
       <c r="H3">
-        <v>-0.02961939840392879</v>
+        <v>0.02233589087809037</v>
       </c>
       <c r="I3">
-        <v>0.002679558011049723</v>
+        <v>-0.03466894003978403</v>
       </c>
       <c r="J3">
-        <v>0.002679558011049723</v>
+        <v>-0.0314909538694705</v>
       </c>
       <c r="K3">
-        <v>7.49</v>
+        <v>14.1</v>
       </c>
       <c r="L3">
-        <v>0.02298956414978514</v>
+        <v>0.04006820119352089</v>
       </c>
       <c r="M3">
-        <v>4.04</v>
+        <v>3.63</v>
       </c>
       <c r="N3">
-        <v>0.03662737987307343</v>
+        <v>0.02510373443983403</v>
       </c>
       <c r="O3">
-        <v>0.5393858477970628</v>
+        <v>0.2574468085106383</v>
       </c>
       <c r="P3">
-        <v>4.04</v>
+        <v>3.63</v>
       </c>
       <c r="Q3">
-        <v>0.03662737987307343</v>
+        <v>0.02510373443983403</v>
       </c>
       <c r="R3">
-        <v>0.5393858477970628</v>
+        <v>0.2574468085106383</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,70 +767,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.62</v>
+        <v>11.5</v>
       </c>
       <c r="V3">
-        <v>0.02375339981867634</v>
+        <v>0.07952973720608576</v>
       </c>
       <c r="W3">
-        <v>0.05404040404040404</v>
+        <v>0.09873949579831932</v>
       </c>
       <c r="X3">
-        <v>0.08539939409945423</v>
+        <v>0.1106899086540348</v>
       </c>
       <c r="Y3">
-        <v>-0.03135899005905018</v>
+        <v>-0.01195041285571549</v>
       </c>
       <c r="Z3">
-        <v>1.542613636363636</v>
+        <v>1.811303273625695</v>
       </c>
       <c r="AA3">
-        <v>0.004133522727272728</v>
+        <v>-0.05703966783336764</v>
       </c>
       <c r="AB3">
-        <v>0.07519238782418403</v>
+        <v>0.1098294225581551</v>
       </c>
       <c r="AC3">
-        <v>-0.0710588650969113</v>
+        <v>-0.1668690903915228</v>
       </c>
       <c r="AD3">
-        <v>54.1</v>
+        <v>8.27</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>54.1</v>
+        <v>8.27</v>
       </c>
       <c r="AG3">
-        <v>51.48</v>
+        <v>-3.23</v>
       </c>
       <c r="AH3">
-        <v>0.3290754257907543</v>
+        <v>0.0540982534179368</v>
       </c>
       <c r="AI3">
-        <v>0.2747587607922803</v>
+        <v>0.0615923139941908</v>
       </c>
       <c r="AJ3">
-        <v>0.3182099146989739</v>
+        <v>-0.02284784607766853</v>
       </c>
       <c r="AK3">
-        <v>0.2649783817171093</v>
+        <v>-0.02630935896391627</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-5.53</v>
+        <v>-0.862</v>
       </c>
       <c r="AN3">
-        <v>10.90725806451613</v>
+        <v>-1.001210653753027</v>
       </c>
       <c r="AP3">
-        <v>10.37903225806452</v>
+        <v>0.391041162227603</v>
       </c>
       <c r="AQ3">
-        <v>-0.1578661844484629</v>
+        <v>14.15313225058004</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/egypt/egypt_power.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_power.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.333</v>
+        <v>0.192</v>
       </c>
       <c r="E2">
-        <v>0.778</v>
+        <v>0.339</v>
       </c>
       <c r="G2">
-        <v>0.02233589087809037</v>
+        <v>-0.03385387618516453</v>
       </c>
       <c r="H2">
-        <v>0.02233589087809037</v>
+        <v>-0.03385387618516453</v>
       </c>
       <c r="I2">
-        <v>-0.03466894003978403</v>
+        <v>-0.0780814277746793</v>
       </c>
       <c r="J2">
-        <v>-0.0314909538694705</v>
+        <v>-0.07158229716872805</v>
       </c>
       <c r="K2">
-        <v>14.1</v>
+        <v>9.32</v>
       </c>
       <c r="L2">
-        <v>0.04006820119352089</v>
+        <v>0.05197992191857222</v>
       </c>
       <c r="M2">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="N2">
-        <v>0.02510373443983403</v>
+        <v>0.02893890675241157</v>
       </c>
       <c r="O2">
-        <v>0.2574468085106383</v>
+        <v>0.3862660944206008</v>
       </c>
       <c r="P2">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="Q2">
-        <v>0.02510373443983403</v>
+        <v>0.02893890675241157</v>
       </c>
       <c r="R2">
-        <v>0.2574468085106383</v>
+        <v>0.3862660944206008</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +636,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="V2">
-        <v>0.07952973720608576</v>
+        <v>0.09967845659163987</v>
       </c>
       <c r="W2">
-        <v>0.09873949579831932</v>
+        <v>0.06238286479250334</v>
       </c>
       <c r="X2">
-        <v>0.1106899086540348</v>
+        <v>0.1090612688150588</v>
       </c>
       <c r="Y2">
-        <v>-0.01195041285571549</v>
+        <v>-0.04667840402255544</v>
       </c>
       <c r="Z2">
-        <v>1.811303273625695</v>
+        <v>1.309715120525931</v>
       </c>
       <c r="AA2">
-        <v>-0.05703966783336764</v>
+        <v>-0.0937524169638637</v>
       </c>
       <c r="AB2">
-        <v>0.1098294225581551</v>
+        <v>0.1089900768681016</v>
       </c>
       <c r="AC2">
-        <v>-0.1668690903915228</v>
+        <v>-0.2027424938319654</v>
       </c>
       <c r="AD2">
-        <v>8.27</v>
+        <v>2.11</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8.27</v>
+        <v>2.11</v>
       </c>
       <c r="AG2">
-        <v>-3.23</v>
+        <v>-10.29</v>
       </c>
       <c r="AH2">
-        <v>0.0540982534179368</v>
+        <v>0.01667852343688246</v>
       </c>
       <c r="AI2">
-        <v>0.0615923139941908</v>
+        <v>0.01591131890505995</v>
       </c>
       <c r="AJ2">
-        <v>-0.02284784607766853</v>
+        <v>-0.09017614582420472</v>
       </c>
       <c r="AK2">
-        <v>-0.02630935896391627</v>
+        <v>-0.08560019965061144</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.862</v>
+        <v>-0.751</v>
       </c>
       <c r="AN2">
-        <v>-1.001210653753027</v>
+        <v>-0.1850877192982456</v>
       </c>
       <c r="AP2">
-        <v>0.391041162227603</v>
+        <v>0.9026315789473685</v>
       </c>
       <c r="AQ2">
-        <v>14.15313225058004</v>
+        <v>18.64181091877496</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.333</v>
+        <v>0.192</v>
       </c>
       <c r="E3">
-        <v>0.778</v>
+        <v>0.339</v>
       </c>
       <c r="G3">
-        <v>0.02233589087809037</v>
+        <v>-0.03385387618516453</v>
       </c>
       <c r="H3">
-        <v>0.02233589087809037</v>
+        <v>-0.03385387618516453</v>
       </c>
       <c r="I3">
-        <v>-0.03466894003978403</v>
+        <v>-0.0780814277746793</v>
       </c>
       <c r="J3">
-        <v>-0.0314909538694705</v>
+        <v>-0.07158229716872805</v>
       </c>
       <c r="K3">
-        <v>14.1</v>
+        <v>9.32</v>
       </c>
       <c r="L3">
-        <v>0.04006820119352089</v>
+        <v>0.05197992191857222</v>
       </c>
       <c r="M3">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="N3">
-        <v>0.02510373443983403</v>
+        <v>0.02893890675241157</v>
       </c>
       <c r="O3">
-        <v>0.2574468085106383</v>
+        <v>0.3862660944206008</v>
       </c>
       <c r="P3">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
-        <v>0.02510373443983403</v>
+        <v>0.02893890675241157</v>
       </c>
       <c r="R3">
-        <v>0.2574468085106383</v>
+        <v>0.3862660944206008</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,70 +767,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="V3">
-        <v>0.07952973720608576</v>
+        <v>0.09967845659163987</v>
       </c>
       <c r="W3">
-        <v>0.09873949579831932</v>
+        <v>0.06238286479250334</v>
       </c>
       <c r="X3">
-        <v>0.1106899086540348</v>
+        <v>0.1090612688150588</v>
       </c>
       <c r="Y3">
-        <v>-0.01195041285571549</v>
+        <v>-0.04667840402255544</v>
       </c>
       <c r="Z3">
-        <v>1.811303273625695</v>
+        <v>1.309715120525931</v>
       </c>
       <c r="AA3">
-        <v>-0.05703966783336764</v>
+        <v>-0.0937524169638637</v>
       </c>
       <c r="AB3">
-        <v>0.1098294225581551</v>
+        <v>0.1089900768681016</v>
       </c>
       <c r="AC3">
-        <v>-0.1668690903915228</v>
+        <v>-0.2027424938319654</v>
       </c>
       <c r="AD3">
-        <v>8.27</v>
+        <v>2.11</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.27</v>
+        <v>2.11</v>
       </c>
       <c r="AG3">
-        <v>-3.23</v>
+        <v>-10.29</v>
       </c>
       <c r="AH3">
-        <v>0.0540982534179368</v>
+        <v>0.01667852343688246</v>
       </c>
       <c r="AI3">
-        <v>0.0615923139941908</v>
+        <v>0.01591131890505995</v>
       </c>
       <c r="AJ3">
-        <v>-0.02284784607766853</v>
+        <v>-0.09017614582420472</v>
       </c>
       <c r="AK3">
-        <v>-0.02630935896391627</v>
+        <v>-0.08560019965061144</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.862</v>
+        <v>-0.751</v>
       </c>
       <c r="AN3">
-        <v>-1.001210653753027</v>
+        <v>-0.1850877192982456</v>
       </c>
       <c r="AP3">
-        <v>0.391041162227603</v>
+        <v>0.9026315789473685</v>
       </c>
       <c r="AQ3">
-        <v>14.15313225058004</v>
+        <v>18.64181091877496</v>
       </c>
     </row>
   </sheetData>
